--- a/AAII_Financials/Quarterly/PETZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PETZ_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/PETZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PETZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
   <si>
     <t>PETZ</t>
   </si>
@@ -656,95 +656,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43646</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43465</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43281</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43100</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>42916</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42735</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42551</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -752,52 +756,55 @@
         <v>1600</v>
       </c>
       <c r="E8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F8" s="3">
         <v>3100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9700</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -805,52 +812,55 @@
         <v>1100</v>
       </c>
       <c r="E9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F9" s="3">
         <v>2000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>300</v>
-      </c>
-      <c r="I9" s="3">
-        <v>400</v>
       </c>
       <c r="J9" s="3">
         <v>400</v>
       </c>
       <c r="K9" s="3">
+        <v>400</v>
+      </c>
+      <c r="L9" s="3">
         <v>6800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7000</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -858,52 +868,55 @@
         <v>500</v>
       </c>
       <c r="E10" s="3">
+        <v>500</v>
+      </c>
+      <c r="F10" s="3">
         <v>1100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-2200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-3200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2700</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -923,8 +936,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -952,32 +966,35 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3">
-        <v>0</v>
+      <c r="L12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>400</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1029,8 +1046,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1041,32 +1061,32 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>800</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>1600</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1082,8 +1102,11 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1135,8 +1158,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1153,114 +1179,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>7100</v>
       </c>
       <c r="E17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F17" s="3">
         <v>6100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9500</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-5500</v>
       </c>
       <c r="E18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>200</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1280,131 +1313,138 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-3000</v>
       </c>
       <c r="E20" s="3">
+        <v>900</v>
+      </c>
+      <c r="F20" s="3">
         <v>4200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
       </c>
       <c r="N20" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>-100</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-8600</v>
       </c>
       <c r="E21" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="F21" s="3">
-        <v>-1200</v>
+        <v>1200</v>
       </c>
       <c r="G21" s="3">
-        <v>-3700</v>
+        <v>-700</v>
       </c>
       <c r="H21" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="I21" s="3">
         <v>-200</v>
       </c>
-      <c r="I21" s="3">
-        <v>1800</v>
-      </c>
       <c r="J21" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K21" s="3">
         <v>-400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>400</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3">
         <v>600</v>
@@ -1413,17 +1453,17 @@
         <v>600</v>
       </c>
       <c r="K22" s="3">
+        <v>600</v>
+      </c>
+      <c r="L22" s="3">
         <v>900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>200</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
@@ -1431,77 +1471,83 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>100</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-8500</v>
       </c>
       <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>200</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1525,28 +1571,31 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1598,114 +1647,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-8500</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>100</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-8600</v>
       </c>
       <c r="E27" s="3">
+        <v>100</v>
+      </c>
+      <c r="F27" s="3">
         <v>1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>100</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1757,37 +1815,40 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-15100</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-300</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="3">
+      <c r="G29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="3">
         <v>-2600</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3">
         <v>-2600</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -1810,8 +1871,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1863,8 +1927,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1916,114 +1983,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>3000</v>
       </c>
       <c r="E32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-4200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
       </c>
       <c r="N32" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>100</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-23700</v>
       </c>
       <c r="E33" s="3">
+        <v>100</v>
+      </c>
+      <c r="F33" s="3">
         <v>800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6100</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-900</v>
       </c>
       <c r="I33" s="3">
         <v>-900</v>
       </c>
       <c r="J33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>100</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2075,119 +2151,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-23700</v>
       </c>
       <c r="E35" s="3">
+        <v>100</v>
+      </c>
+      <c r="F35" s="3">
         <v>800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6100</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-900</v>
       </c>
       <c r="I35" s="3">
         <v>-900</v>
       </c>
       <c r="J35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>100</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43646</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43465</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43281</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43100</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>42916</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42735</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42551</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2207,8 +2292,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2228,88 +2314,92 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E41" s="3">
         <v>18000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>21900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>500</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E42" s="3">
         <v>13000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>9900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>11600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8200</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2325,8 +2415,8 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2334,8 +2424,11 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2355,40 +2448,43 @@
         <v>0</v>
       </c>
       <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
         <v>200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>1900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1700</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2402,152 +2498,161 @@
         <v>0</v>
       </c>
       <c r="G44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H44" s="3">
         <v>100</v>
       </c>
       <c r="I44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J44" s="3">
         <v>200</v>
       </c>
       <c r="K44" s="3">
+        <v>200</v>
+      </c>
+      <c r="L44" s="3">
         <v>500</v>
-      </c>
-      <c r="L44" s="3">
-        <v>3000</v>
       </c>
       <c r="M44" s="3">
         <v>3000</v>
       </c>
       <c r="N44" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O44" s="3">
         <v>7700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>9100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>9300</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="E45" s="3">
         <v>2000</v>
       </c>
       <c r="F45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G45" s="3">
         <v>1600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1700</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E46" s="3">
         <v>33000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>33800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>25400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>31100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13200</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2569,14 +2674,14 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
-        <v>100</v>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>100</v>
       </c>
       <c r="L47" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M47" s="3">
         <v>200</v>
@@ -2584,8 +2689,8 @@
       <c r="N47" s="3">
         <v>200</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
+      <c r="O47" s="3">
+        <v>200</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
@@ -2599,87 +2704,93 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3200</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E49" s="3">
         <v>500</v>
       </c>
       <c r="F49" s="3">
+        <v>500</v>
+      </c>
+      <c r="G49" s="3">
         <v>600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>900</v>
-      </c>
-      <c r="K49" s="3">
-        <v>1000</v>
       </c>
       <c r="L49" s="3">
         <v>1000</v>
@@ -2688,25 +2799,28 @@
         <v>1000</v>
       </c>
       <c r="N49" s="3">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="O49" s="3">
         <v>200</v>
       </c>
       <c r="P49" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q49" s="3">
         <v>100</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2758,8 +2872,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2811,26 +2928,29 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
         <v>700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>800</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
         <v>900</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2840,21 +2960,21 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>1400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>500</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2864,8 +2984,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2917,61 +3040,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E54" s="3">
         <v>35600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>28400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>37900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>18800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>19800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16600</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2991,8 +3120,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3012,8 +3142,9 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3024,69 +3155,72 @@
         <v>500</v>
       </c>
       <c r="F57" s="3">
+        <v>500</v>
+      </c>
+      <c r="G57" s="3">
         <v>2900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>3200</v>
       </c>
       <c r="I57" s="3">
         <v>3200</v>
       </c>
       <c r="J57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K57" s="3">
         <v>3100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E58" s="3">
         <v>300</v>
       </c>
       <c r="F58" s="3">
-        <v>5800</v>
+        <v>300</v>
       </c>
       <c r="G58" s="3">
         <v>5800</v>
       </c>
       <c r="H58" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I58" s="3">
         <v>6400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>9500</v>
       </c>
       <c r="J58" s="3">
         <v>9500</v>
@@ -3095,137 +3229,146 @@
         <v>9500</v>
       </c>
       <c r="L58" s="3">
+        <v>9500</v>
+      </c>
+      <c r="M58" s="3">
         <v>15200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3700</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E59" s="3">
         <v>11900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1100</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E60" s="3">
         <v>12700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>20700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>19100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11000</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3254,13 +3397,13 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M61" s="3">
         <v>200</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -3277,25 +3420,28 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>500</v>
+      </c>
+      <c r="E62" s="3">
         <v>600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>300</v>
       </c>
       <c r="I62" s="3">
         <v>300</v>
@@ -3310,7 +3456,7 @@
         <v>300</v>
       </c>
       <c r="M62" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -3321,8 +3467,8 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
+      <c r="Q62" s="3">
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
@@ -3330,8 +3476,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3383,8 +3532,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3436,8 +3588,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3489,61 +3644,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E66" s="3">
         <v>13600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>15800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>19300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>21300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11000</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3563,8 +3724,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3616,8 +3778,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3669,8 +3834,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3722,8 +3890,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3775,61 +3946,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-27900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-28000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-29700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-28800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-23600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-22700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-22400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-21800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-14900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-13200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1400</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3881,8 +4058,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3934,8 +4114,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3987,61 +4170,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E76" s="3">
         <v>21900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-2700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-1900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5600</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4093,119 +4282,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43646</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43465</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43281</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43100</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>42916</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42735</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42551</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-23700</v>
       </c>
       <c r="E81" s="3">
+        <v>100</v>
+      </c>
+      <c r="F81" s="3">
         <v>800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6100</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-900</v>
       </c>
       <c r="I81" s="3">
         <v>-900</v>
       </c>
       <c r="J81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>100</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4225,40 +4423,41 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>-200</v>
+        <v>500</v>
       </c>
       <c r="I83" s="3">
-        <v>-200</v>
+        <v>200</v>
       </c>
       <c r="J83" s="3">
+        <v>400</v>
+      </c>
+      <c r="K83" s="3">
         <v>-400</v>
-      </c>
-      <c r="K83" s="3">
-        <v>300</v>
       </c>
       <c r="L83" s="3">
         <v>300</v>
       </c>
       <c r="M83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N83" s="3">
         <v>200</v>
@@ -4270,16 +4469,19 @@
         <v>200</v>
       </c>
       <c r="Q83" s="3">
+        <v>200</v>
+      </c>
+      <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4331,8 +4533,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4384,8 +4589,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4437,8 +4645,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4490,8 +4701,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4543,61 +4757,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-100</v>
       </c>
       <c r="E89" s="3">
-        <v>1200</v>
+        <v>-2300</v>
       </c>
       <c r="F89" s="3">
-        <v>2400</v>
+        <v>-2100</v>
       </c>
       <c r="G89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="K89" s="3">
+        <v>4800</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="P89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-1100</v>
       </c>
-      <c r="H89" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="I89" s="3">
-        <v>3500</v>
-      </c>
-      <c r="J89" s="3">
-        <v>4800</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="R89" s="3">
         <v>-900</v>
       </c>
-      <c r="L89" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-900</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-600</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4617,8 +4837,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4641,37 +4862,40 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M91" s="3">
         <v>-6400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4723,8 +4947,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4776,61 +5003,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-3900</v>
       </c>
       <c r="E94" s="3">
-        <v>300</v>
+        <v>-2200</v>
       </c>
       <c r="F94" s="3">
-        <v>-4400</v>
+        <v>-1300</v>
       </c>
       <c r="G94" s="3">
-        <v>-5000</v>
+        <v>-6100</v>
       </c>
       <c r="H94" s="3">
-        <v>2500</v>
+        <v>-1600</v>
       </c>
       <c r="I94" s="3">
-        <v>3200</v>
+        <v>5800</v>
       </c>
       <c r="J94" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-4600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-6300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4850,8 +5083,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4903,8 +5137,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4956,8 +5193,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5009,8 +5249,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5062,97 +5305,103 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E100" s="3">
-        <v>-12000</v>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F100" s="3">
-        <v>-18100</v>
+        <v>6100</v>
       </c>
       <c r="G100" s="3">
-        <v>18700</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>200</v>
+        <v>18100</v>
       </c>
       <c r="I100" s="3">
-        <v>-10100</v>
+        <v>-400</v>
       </c>
       <c r="J100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K100" s="3">
         <v>-9400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>6000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>-2100</v>
       </c>
       <c r="E101" s="3">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="F101" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="G101" s="3">
-        <v>-400</v>
+        <v>1100</v>
       </c>
       <c r="H101" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="I101" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J101" s="3">
+        <v>100</v>
+      </c>
+      <c r="K101" s="3">
         <v>200</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-100</v>
       </c>
       <c r="L101" s="3">
         <v>-100</v>
       </c>
       <c r="M101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
@@ -5165,60 +5414,66 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>-4200</v>
       </c>
       <c r="E102" s="3">
-        <v>-9100</v>
+        <v>-4000</v>
       </c>
       <c r="F102" s="3">
-        <v>-18600</v>
+        <v>3600</v>
       </c>
       <c r="G102" s="3">
-        <v>12500</v>
+        <v>-5900</v>
       </c>
       <c r="H102" s="3">
+        <v>12800</v>
+      </c>
+      <c r="I102" s="3">
+        <v>600</v>
+      </c>
+      <c r="J102" s="3">
+        <v>200</v>
+      </c>
+      <c r="K102" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="L102" s="3">
+        <v>3400</v>
+      </c>
+      <c r="M102" s="3">
         <v>400</v>
       </c>
-      <c r="I102" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="K102" s="3">
-        <v>3400</v>
-      </c>
-      <c r="L102" s="3">
-        <v>400</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-300</v>
       </c>
-      <c r="S102" s="3" t="s">
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PETZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PETZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
   <si>
     <t>PETZ</t>
   </si>
@@ -662,14 +662,11 @@
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -700,22 +697,22 @@
         <v>45291</v>
       </c>
       <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>44834</v>
+      </c>
+      <c r="J7" s="2">
         <v>44742</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44377</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44196</v>
       </c>
       <c r="K7" s="2">
         <v>44012</v>
@@ -753,25 +750,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="E8" s="3">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="F8" s="3">
-        <v>3100</v>
+        <v>800</v>
       </c>
       <c r="G8" s="3">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="H8" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="I8" s="3">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="J8" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="K8" s="3">
         <v>300</v>
@@ -809,25 +806,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="E9" s="3">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="F9" s="3">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="G9" s="3">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="H9" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="I9" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="J9" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="K9" s="3">
         <v>400</v>
@@ -865,22 +862,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E10" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F10" s="3">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="G10" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H10" s="3">
         <v>300</v>
       </c>
       <c r="I10" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="J10" s="3">
         <v>200</v>
@@ -1055,25 +1052,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-400</v>
+        <v>1300</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="I14" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1186,25 +1183,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7100</v>
+        <v>3500</v>
       </c>
       <c r="E17" s="3">
-        <v>2400</v>
+        <v>3500</v>
       </c>
       <c r="F17" s="3">
-        <v>6100</v>
+        <v>1200</v>
       </c>
       <c r="G17" s="3">
-        <v>3300</v>
+        <v>1200</v>
       </c>
       <c r="H17" s="3">
-        <v>4700</v>
+        <v>1300</v>
       </c>
       <c r="I17" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="J17" s="3">
-        <v>1100</v>
+        <v>1900</v>
       </c>
       <c r="K17" s="3">
         <v>1300</v>
@@ -1242,25 +1239,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-5500</v>
+        <v>-2700</v>
       </c>
       <c r="E18" s="3">
-        <v>-800</v>
+        <v>-2700</v>
       </c>
       <c r="F18" s="3">
-        <v>-3000</v>
+        <v>-400</v>
       </c>
       <c r="G18" s="3">
-        <v>-1800</v>
+        <v>-400</v>
       </c>
       <c r="H18" s="3">
-        <v>-3600</v>
+        <v>-400</v>
       </c>
       <c r="I18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-500</v>
       </c>
       <c r="K18" s="3">
         <v>-1000</v>
@@ -1320,25 +1317,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-3000</v>
+        <v>-200</v>
       </c>
       <c r="E20" s="3">
-        <v>900</v>
+        <v>-200</v>
       </c>
       <c r="F20" s="3">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>900</v>
@@ -1376,25 +1373,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-8600</v>
+        <v>-2500</v>
       </c>
       <c r="E21" s="3">
-        <v>100</v>
+        <v>-2500</v>
       </c>
       <c r="F21" s="3">
-        <v>1200</v>
+        <v>-400</v>
       </c>
       <c r="G21" s="3">
-        <v>-700</v>
+        <v>-400</v>
       </c>
       <c r="H21" s="3">
-        <v>-3600</v>
+        <v>-400</v>
       </c>
       <c r="I21" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="J21" s="3">
-        <v>2400</v>
+        <v>-1100</v>
       </c>
       <c r="K21" s="3">
         <v>-400</v>
@@ -1431,26 +1428,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>0</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
+      <c r="F22" s="3">
+        <v>0</v>
       </c>
       <c r="G22" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
       <c r="I22" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="K22" s="3">
         <v>600</v>
@@ -1488,25 +1485,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-8500</v>
+        <v>-4300</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="F23" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="G23" s="3">
-        <v>-1300</v>
+        <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>-4100</v>
+        <v>900</v>
       </c>
       <c r="I23" s="3">
-        <v>-900</v>
+        <v>900</v>
       </c>
       <c r="J23" s="3">
-        <v>1700</v>
+        <v>-700</v>
       </c>
       <c r="K23" s="3">
         <v>-600</v>
@@ -1549,20 +1546,20 @@
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1656,25 +1653,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-8500</v>
+        <v>-4300</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="F26" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="G26" s="3">
-        <v>-1300</v>
+        <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>-4100</v>
+        <v>900</v>
       </c>
       <c r="I26" s="3">
-        <v>-900</v>
+        <v>900</v>
       </c>
       <c r="J26" s="3">
-        <v>1700</v>
+        <v>-700</v>
       </c>
       <c r="K26" s="3">
         <v>-600</v>
@@ -1712,25 +1709,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-8600</v>
+        <v>-11800</v>
       </c>
       <c r="E27" s="3">
-        <v>100</v>
+        <v>-11800</v>
       </c>
       <c r="F27" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="G27" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>-3500</v>
+        <v>800</v>
       </c>
       <c r="I27" s="3">
-        <v>-900</v>
+        <v>800</v>
       </c>
       <c r="J27" s="3">
-        <v>1700</v>
+        <v>-400</v>
       </c>
       <c r="K27" s="3">
         <v>-600</v>
@@ -1824,25 +1821,25 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-15100</v>
+        <v>-7500</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>-7500</v>
       </c>
       <c r="F29" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="I29" s="3">
+        <v>100</v>
       </c>
       <c r="J29" s="3">
-        <v>-2600</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1992,25 +1989,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="E32" s="3">
-        <v>-900</v>
+        <v>200</v>
       </c>
       <c r="F32" s="3">
-        <v>-4200</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>-2800</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>-900</v>
@@ -2048,25 +2045,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-23700</v>
+        <v>-11800</v>
       </c>
       <c r="E33" s="3">
-        <v>100</v>
+        <v>-11800</v>
       </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>800</v>
       </c>
-      <c r="G33" s="3">
-        <v>-900</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-6100</v>
-      </c>
       <c r="I33" s="3">
-        <v>-900</v>
+        <v>800</v>
       </c>
       <c r="J33" s="3">
-        <v>-900</v>
+        <v>-400</v>
       </c>
       <c r="K33" s="3">
         <v>-600</v>
@@ -2160,25 +2157,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-23700</v>
+        <v>-11800</v>
       </c>
       <c r="E35" s="3">
-        <v>100</v>
+        <v>-11800</v>
       </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>800</v>
       </c>
-      <c r="G35" s="3">
-        <v>-900</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-6100</v>
-      </c>
       <c r="I35" s="3">
-        <v>-900</v>
+        <v>800</v>
       </c>
       <c r="J35" s="3">
-        <v>-900</v>
+        <v>-400</v>
       </c>
       <c r="K35" s="3">
         <v>-600</v>
@@ -2224,22 +2221,22 @@
         <v>45291</v>
       </c>
       <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>44834</v>
+      </c>
+      <c r="J38" s="2">
         <v>44742</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44377</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44196</v>
       </c>
       <c r="K38" s="2">
         <v>44012</v>
@@ -2324,22 +2321,22 @@
         <v>13700</v>
       </c>
       <c r="E41" s="3">
+        <v>13700</v>
+      </c>
+      <c r="F41" s="3">
         <v>18000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
+        <v>18000</v>
+      </c>
+      <c r="H41" s="3">
         <v>21900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
+        <v>21900</v>
+      </c>
+      <c r="J41" s="3">
         <v>12200</v>
-      </c>
-      <c r="H41" s="3">
-        <v>18000</v>
-      </c>
-      <c r="I41" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J41" s="3">
-        <v>6600</v>
       </c>
       <c r="K41" s="3">
         <v>500</v>
@@ -2380,22 +2377,22 @@
         <v>13300</v>
       </c>
       <c r="E42" s="3">
+        <v>13300</v>
+      </c>
+      <c r="F42" s="3">
         <v>13000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
+        <v>13000</v>
+      </c>
+      <c r="H42" s="3">
         <v>9900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
+        <v>9900</v>
+      </c>
+      <c r="J42" s="3">
         <v>11600</v>
-      </c>
-      <c r="H42" s="3">
-        <v>4400</v>
-      </c>
-      <c r="I42" s="3">
-        <v>4500</v>
-      </c>
-      <c r="J42" s="3">
-        <v>3100</v>
       </c>
       <c r="K42" s="3">
         <v>8200</v>
@@ -2451,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K43" s="3">
         <v>100</v>
@@ -2494,20 +2491,20 @@
       <c r="E44" s="3">
         <v>0</v>
       </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J44" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K44" s="3">
         <v>200</v>
@@ -2548,22 +2545,22 @@
         <v>200</v>
       </c>
       <c r="E45" s="3">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="F45" s="3">
         <v>2000</v>
       </c>
       <c r="G45" s="3">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="H45" s="3">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="I45" s="3">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="J45" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="K45" s="3">
         <v>1200</v>
@@ -2604,22 +2601,22 @@
         <v>27200</v>
       </c>
       <c r="E46" s="3">
+        <v>27200</v>
+      </c>
+      <c r="F46" s="3">
         <v>33000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
+        <v>33000</v>
+      </c>
+      <c r="H46" s="3">
         <v>33800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
+        <v>33800</v>
+      </c>
+      <c r="J46" s="3">
         <v>25400</v>
-      </c>
-      <c r="H46" s="3">
-        <v>31100</v>
-      </c>
-      <c r="I46" s="3">
-        <v>12200</v>
-      </c>
-      <c r="J46" s="3">
-        <v>10500</v>
       </c>
       <c r="K46" s="3">
         <v>10200</v>
@@ -2716,22 +2713,22 @@
         <v>1300</v>
       </c>
       <c r="E48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F48" s="3">
         <v>1400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H48" s="3">
         <v>1500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J48" s="3">
         <v>2300</v>
-      </c>
-      <c r="H48" s="3">
-        <v>5400</v>
-      </c>
-      <c r="I48" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J48" s="3">
-        <v>6900</v>
       </c>
       <c r="K48" s="3">
         <v>6500</v>
@@ -2772,22 +2769,22 @@
         <v>400</v>
       </c>
       <c r="E49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F49" s="3">
         <v>500</v>
       </c>
       <c r="G49" s="3">
+        <v>500</v>
+      </c>
+      <c r="H49" s="3">
+        <v>500</v>
+      </c>
+      <c r="I49" s="3">
+        <v>500</v>
+      </c>
+      <c r="J49" s="3">
         <v>600</v>
-      </c>
-      <c r="H49" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I49" s="3">
-        <v>200</v>
-      </c>
-      <c r="J49" s="3">
-        <v>1000</v>
       </c>
       <c r="K49" s="3">
         <v>900</v>
@@ -2936,23 +2933,23 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3">
         <v>700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
+        <v>700</v>
+      </c>
+      <c r="H52" s="3">
         <v>800</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3">
-        <v>900</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="I52" s="3">
+        <v>800</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -3052,22 +3049,22 @@
         <v>28900</v>
       </c>
       <c r="E54" s="3">
+        <v>28900</v>
+      </c>
+      <c r="F54" s="3">
         <v>35600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
+        <v>35600</v>
+      </c>
+      <c r="H54" s="3">
         <v>36500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>36500</v>
+      </c>
+      <c r="J54" s="3">
         <v>28400</v>
-      </c>
-      <c r="H54" s="3">
-        <v>37900</v>
-      </c>
-      <c r="I54" s="3">
-        <v>13800</v>
-      </c>
-      <c r="J54" s="3">
-        <v>18500</v>
       </c>
       <c r="K54" s="3">
         <v>17700</v>
@@ -3158,16 +3155,16 @@
         <v>500</v>
       </c>
       <c r="G57" s="3">
-        <v>2900</v>
+        <v>500</v>
       </c>
       <c r="H57" s="3">
         <v>500</v>
       </c>
       <c r="I57" s="3">
-        <v>3200</v>
+        <v>500</v>
       </c>
       <c r="J57" s="3">
-        <v>3200</v>
+        <v>3000</v>
       </c>
       <c r="K57" s="3">
         <v>3100</v>
@@ -3205,25 +3202,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E58" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F58" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G58" s="3">
-        <v>5800</v>
+        <v>500</v>
       </c>
       <c r="H58" s="3">
-        <v>5800</v>
+        <v>600</v>
       </c>
       <c r="I58" s="3">
-        <v>6400</v>
+        <v>600</v>
       </c>
       <c r="J58" s="3">
-        <v>9500</v>
+        <v>6000</v>
       </c>
       <c r="K58" s="3">
         <v>9500</v>
@@ -3261,25 +3258,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2600</v>
+        <v>2200</v>
       </c>
       <c r="E59" s="3">
-        <v>11900</v>
+        <v>2200</v>
       </c>
       <c r="F59" s="3">
-        <v>13800</v>
+        <v>11700</v>
       </c>
       <c r="G59" s="3">
-        <v>4800</v>
+        <v>11700</v>
       </c>
       <c r="H59" s="3">
-        <v>18800</v>
+        <v>13500</v>
       </c>
       <c r="I59" s="3">
-        <v>3100</v>
+        <v>13500</v>
       </c>
       <c r="J59" s="3">
-        <v>6400</v>
+        <v>4500</v>
       </c>
       <c r="K59" s="3">
         <v>5000</v>
@@ -3320,22 +3317,22 @@
         <v>3400</v>
       </c>
       <c r="E60" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F60" s="3">
         <v>12700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
+        <v>12700</v>
+      </c>
+      <c r="H60" s="3">
         <v>14700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>14700</v>
+      </c>
+      <c r="J60" s="3">
         <v>13500</v>
-      </c>
-      <c r="H60" s="3">
-        <v>19700</v>
-      </c>
-      <c r="I60" s="3">
-        <v>12700</v>
-      </c>
-      <c r="J60" s="3">
-        <v>19100</v>
       </c>
       <c r="K60" s="3">
         <v>17600</v>
@@ -3373,25 +3370,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3428,26 +3425,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>600</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F62" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3">
-        <v>300</v>
-      </c>
-      <c r="J62" s="3">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>300</v>
@@ -3653,25 +3650,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4300</v>
+        <v>3900</v>
       </c>
       <c r="E66" s="3">
-        <v>13600</v>
+        <v>3900</v>
       </c>
       <c r="F66" s="3">
-        <v>15800</v>
+        <v>13300</v>
       </c>
       <c r="G66" s="3">
-        <v>14900</v>
+        <v>13300</v>
       </c>
       <c r="H66" s="3">
-        <v>24900</v>
+        <v>15400</v>
       </c>
       <c r="I66" s="3">
-        <v>13000</v>
+        <v>15400</v>
       </c>
       <c r="J66" s="3">
-        <v>19300</v>
+        <v>14300</v>
       </c>
       <c r="K66" s="3">
         <v>17900</v>
@@ -3958,22 +3955,22 @@
         <v>-26600</v>
       </c>
       <c r="E72" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-27900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="H72" s="3">
         <v>-28000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="J72" s="3">
         <v>-29700</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-28800</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-23600</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-22700</v>
       </c>
       <c r="K72" s="3">
         <v>-22400</v>
@@ -4182,22 +4179,22 @@
         <v>24600</v>
       </c>
       <c r="E76" s="3">
+        <v>24600</v>
+      </c>
+      <c r="F76" s="3">
         <v>21900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>21900</v>
+      </c>
+      <c r="H76" s="3">
         <v>20700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>20700</v>
+      </c>
+      <c r="J76" s="3">
         <v>13500</v>
-      </c>
-      <c r="H76" s="3">
-        <v>13000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>800</v>
-      </c>
-      <c r="J76" s="3">
-        <v>-900</v>
       </c>
       <c r="K76" s="3">
         <v>-200</v>
@@ -4299,22 +4296,22 @@
         <v>45291</v>
       </c>
       <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>44834</v>
+      </c>
+      <c r="J80" s="2">
         <v>44742</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44377</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44196</v>
       </c>
       <c r="K80" s="2">
         <v>44012</v>
@@ -4352,25 +4349,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-23700</v>
+        <v>-11800</v>
       </c>
       <c r="E81" s="3">
-        <v>100</v>
+        <v>-11800</v>
       </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>800</v>
       </c>
-      <c r="G81" s="3">
-        <v>-900</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-6100</v>
-      </c>
       <c r="I81" s="3">
-        <v>-900</v>
+        <v>800</v>
       </c>
       <c r="J81" s="3">
-        <v>-900</v>
+        <v>-400</v>
       </c>
       <c r="K81" s="3">
         <v>-600</v>
@@ -4433,22 +4430,22 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3">
         <v>100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>200</v>
-      </c>
-      <c r="J83" s="3">
-        <v>400</v>
       </c>
       <c r="K83" s="3">
         <v>-400</v>
@@ -4769,22 +4766,22 @@
         <v>-100</v>
       </c>
       <c r="E89" s="3">
-        <v>-2300</v>
+        <v>-100</v>
       </c>
       <c r="F89" s="3">
-        <v>-2100</v>
+        <v>-1200</v>
       </c>
       <c r="G89" s="3">
-        <v>-900</v>
+        <v>-1200</v>
       </c>
       <c r="H89" s="3">
-        <v>-3300</v>
+        <v>-600</v>
       </c>
       <c r="I89" s="3">
-        <v>-4800</v>
+        <v>-600</v>
       </c>
       <c r="J89" s="3">
-        <v>-2200</v>
+        <v>-400</v>
       </c>
       <c r="K89" s="3">
         <v>4800</v>
@@ -4849,20 +4846,20 @@
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
@@ -5012,25 +5009,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3900</v>
+        <v>-2000</v>
       </c>
       <c r="E94" s="3">
-        <v>-2200</v>
+        <v>-2000</v>
       </c>
       <c r="F94" s="3">
-        <v>-1300</v>
+        <v>-1100</v>
       </c>
       <c r="G94" s="3">
-        <v>-6100</v>
+        <v>-1100</v>
       </c>
       <c r="H94" s="3">
-        <v>-1600</v>
+        <v>2400</v>
       </c>
       <c r="I94" s="3">
-        <v>5800</v>
+        <v>2400</v>
       </c>
       <c r="J94" s="3">
-        <v>3400</v>
+        <v>-3000</v>
       </c>
       <c r="K94" s="3">
         <v>-4600</v>
@@ -5089,26 +5086,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5313,26 +5310,26 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3">
-        <v>6100</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
+      <c r="D100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H100" s="3">
-        <v>18100</v>
+        <v>3000</v>
       </c>
       <c r="I100" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-600</v>
+        <v>3000</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>-9400</v>
@@ -5370,25 +5367,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-2100</v>
+        <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
-        <v>1000</v>
-      </c>
       <c r="G101" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K101" s="3">
         <v>200</v>
@@ -5426,25 +5423,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-4200</v>
+        <v>-2100</v>
       </c>
       <c r="E102" s="3">
-        <v>-4000</v>
+        <v>-2100</v>
       </c>
       <c r="F102" s="3">
-        <v>3600</v>
+        <v>-2000</v>
       </c>
       <c r="G102" s="3">
-        <v>-5900</v>
+        <v>-2000</v>
       </c>
       <c r="H102" s="3">
-        <v>12800</v>
+        <v>4800</v>
       </c>
       <c r="I102" s="3">
-        <v>600</v>
+        <v>4800</v>
       </c>
       <c r="J102" s="3">
-        <v>200</v>
+        <v>-2900</v>
       </c>
       <c r="K102" s="3">
         <v>-8900</v>

--- a/AAII_Financials/Quarterly/PETZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PETZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
   <si>
     <t>PETZ</t>
   </si>
@@ -656,104 +656,112 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43646</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43281</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>42916</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>42735</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42551</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
-        <v>800</v>
+      <c r="D8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E8" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="F8" s="3">
         <v>800</v>
@@ -768,48 +776,54 @@
         <v>800</v>
       </c>
       <c r="J8" s="3">
+        <v>800</v>
+      </c>
+      <c r="K8" s="3">
+        <v>800</v>
+      </c>
+      <c r="L8" s="3">
         <v>700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>4600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>8000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>12100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>11600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>14900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>14100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>14700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>9700</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3">
         <v>500</v>
@@ -827,93 +841,105 @@
         <v>500</v>
       </c>
       <c r="K9" s="3">
+        <v>500</v>
+      </c>
+      <c r="L9" s="3">
+        <v>500</v>
+      </c>
+      <c r="M9" s="3">
         <v>400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>6800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>7400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>15300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>12400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>10800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>9900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>10400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>7000</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
         <v>300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>-2200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>-3200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>-800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>4100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>4200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>4300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>2700</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,8 +960,10 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -966,32 +994,38 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3">
         <v>100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>400</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1046,50 +1080,56 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>200</v>
+      </c>
+      <c r="F14" s="3">
         <v>1300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>1300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>800</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>1600</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1102,8 +1142,14 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1158,8 +1204,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1177,78 +1229,86 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>400</v>
+      </c>
+      <c r="F17" s="3">
         <v>3500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1300</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1900</v>
       </c>
       <c r="K17" s="3">
         <v>1300</v>
       </c>
       <c r="L17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N17" s="3">
         <v>10300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>9300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>20500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>17200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>15300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>13400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>13800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>9500</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2700</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-400</v>
       </c>
       <c r="H18" s="3">
         <v>-400</v>
@@ -1257,40 +1317,46 @@
         <v>-400</v>
       </c>
       <c r="J18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L18" s="3">
         <v>-1100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-5700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-8400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-5600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>200</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1311,23 +1377,25 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1338,51 +1406,57 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-2500</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-400</v>
       </c>
       <c r="H21" s="3">
         <v>-400</v>
@@ -1391,40 +1465,46 @@
         <v>-400</v>
       </c>
       <c r="J21" s="3">
-        <v>-1100</v>
+        <v>-400</v>
       </c>
       <c r="K21" s="3">
         <v>-400</v>
       </c>
       <c r="L21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N21" s="3">
         <v>-5800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-8100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-5500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>400</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1447,96 +1527,108 @@
         <v>0</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>200</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-4300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-4300</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-7000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-8500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-5700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>200</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1561,38 +1653,44 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>100</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
       </c>
       <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>100</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1647,120 +1745,138 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-4300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-4300</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-7000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-9400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-4800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>100</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-11800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-11800</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-7000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-9400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-4800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>100</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1815,43 +1931,49 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F29" s="3">
         <v>-7500</v>
       </c>
-      <c r="E29" s="3">
+      <c r="G29" s="3">
         <v>-7500</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>100</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -1871,8 +1993,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1927,8 +2055,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1983,23 +2117,29 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -2010,93 +2150,105 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-11800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-11800</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-7000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-9400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-4800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>100</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2151,125 +2303,143 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-11800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-11800</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-7000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-9400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-4800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>100</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43646</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43281</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>42916</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>42735</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42551</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2290,8 +2460,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2312,97 +2484,105 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>12900</v>
+      </c>
+      <c r="F41" s="3">
         <v>13700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>13700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>18000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>18000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>21900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>21900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>12200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>5100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>500</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F42" s="3">
         <v>13300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>13300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>13000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>13000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>9900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>9900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>11600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>8200</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2415,17 +2595,23 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2451,93 +2637,105 @@
         <v>0</v>
       </c>
       <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
         <v>1900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>2300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1700</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J44" s="3">
         <v>0</v>
       </c>
       <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
         <v>200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>3000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>3000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>7700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>9100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>9300</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2548,10 +2746,10 @@
         <v>200</v>
       </c>
       <c r="F45" s="3">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="G45" s="3">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="H45" s="3">
         <v>2000</v>
@@ -2560,96 +2758,108 @@
         <v>2000</v>
       </c>
       <c r="J45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>2400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1700</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>25600</v>
+      </c>
+      <c r="F46" s="3">
         <v>27200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>27200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>33000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>33000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>33800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>33800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>25400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>10200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>7200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>8700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>7800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>13700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>15600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>13200</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2674,26 +2884,26 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>100</v>
-      </c>
-      <c r="M47" s="3">
-        <v>200</v>
-      </c>
-      <c r="N47" s="3">
-        <v>200</v>
       </c>
       <c r="O47" s="3">
         <v>200</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>200</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -2704,78 +2914,90 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F48" s="3">
         <v>1300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>6500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>6800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>8600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>8400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3200</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>400</v>
-      </c>
-      <c r="F49" s="3">
-        <v>500</v>
-      </c>
-      <c r="G49" s="3">
-        <v>500</v>
       </c>
       <c r="H49" s="3">
         <v>500</v>
@@ -2784,40 +3006,46 @@
         <v>500</v>
       </c>
       <c r="J49" s="3">
+        <v>500</v>
+      </c>
+      <c r="K49" s="3">
+        <v>500</v>
+      </c>
+      <c r="L49" s="3">
         <v>600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>900</v>
-      </c>
-      <c r="L49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1000</v>
       </c>
       <c r="N49" s="3">
         <v>1000</v>
       </c>
       <c r="O49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q49" s="3">
         <v>200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>100</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2872,8 +3100,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3162,14 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2939,53 +3179,59 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
         <v>700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>800</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>500</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3040,64 +3286,76 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>30600</v>
+      </c>
+      <c r="F54" s="3">
         <v>28900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>28900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>35600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>35600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>36500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>36500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>28400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>17700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>15100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>18500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>17400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>18800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>19800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>16600</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,8 +3376,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3140,16 +3400,18 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F57" s="3">
         <v>500</v>
@@ -3164,250 +3426,274 @@
         <v>500</v>
       </c>
       <c r="J57" s="3">
+        <v>500</v>
+      </c>
+      <c r="K57" s="3">
+        <v>500</v>
+      </c>
+      <c r="L57" s="3">
         <v>3000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>6200</v>
-      </c>
-      <c r="O57" s="3">
-        <v>6300</v>
-      </c>
-      <c r="P57" s="3">
-        <v>4700</v>
       </c>
       <c r="Q57" s="3">
         <v>6300</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
+      <c r="R57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="S57" s="3">
+        <v>6300</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>900</v>
+      </c>
+      <c r="F58" s="3">
         <v>600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>6000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>9500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>9500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>15200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>11900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>5100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>3100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>3700</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F59" s="3">
         <v>2200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>11700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>11700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>13500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>13500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>4500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1100</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F60" s="3">
         <v>3400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>12700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>12700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>14700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>14700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>13500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>17600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>14500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>20700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>19100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>12400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>8700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>11000</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F61" s="3">
         <v>500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>800</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>200</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3420,8 +3706,14 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3431,11 +3723,11 @@
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
         <v>0</v>
@@ -3443,23 +3735,23 @@
       <c r="I62" s="3">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+      <c r="J62" s="3">
+        <v>0</v>
       </c>
       <c r="K62" s="3">
-        <v>300</v>
-      </c>
-      <c r="L62" s="3">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>300</v>
       </c>
       <c r="N62" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O62" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -3467,17 +3759,23 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
+        <v>0</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3532,8 +3830,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3588,8 +3892,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3644,64 +3954,76 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F66" s="3">
         <v>3900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>13300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>13300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>15400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>15400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>14300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>17900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>14700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>21300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>19400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>12400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>8700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>11000</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3722,8 +4044,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3778,8 +4102,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3834,8 +4164,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3890,8 +4226,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3946,64 +4288,76 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-26600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-26600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-27900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-27900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-28000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-28000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-29700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-22400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-21800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-14900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-13200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-3800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1400</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4058,8 +4412,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4114,8 +4474,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4170,64 +4536,76 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>25900</v>
+      </c>
+      <c r="F76" s="3">
         <v>24600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>24600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>21900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>21900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>20700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>20700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>13500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-2700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-1900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>6500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>11100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>5600</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4282,125 +4660,143 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43646</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43281</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>42916</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>42735</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42551</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-11800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-11800</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-7000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-9400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-4800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>100</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4421,16 +4817,18 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -4438,29 +4836,29 @@
       <c r="G83" s="3">
         <v>0</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>-400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>300</v>
-      </c>
-      <c r="N83" s="3">
-        <v>200</v>
-      </c>
-      <c r="O83" s="3">
-        <v>200</v>
       </c>
       <c r="P83" s="3">
         <v>200</v>
@@ -4469,16 +4867,22 @@
         <v>200</v>
       </c>
       <c r="R83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>100</v>
+      </c>
+      <c r="U83" s="3">
+        <v>200</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4533,8 +4937,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4589,8 +4999,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4645,8 +5061,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4701,8 +5123,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4757,64 +5185,76 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>4800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-4700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-600</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4835,22 +5275,24 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
+        <v>-900</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -4861,38 +5303,44 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-6400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-5600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4947,8 +5395,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5003,64 +5457,76 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-2000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>2400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>2400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-3000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-4600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-6300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>1200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5081,8 +5547,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5107,11 +5575,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5137,8 +5605,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5193,8 +5667,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5249,8 +5729,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5305,106 +5791,118 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
         <v>1000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1000</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>3000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>3000</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>-9400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>4200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>5300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>6000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>1700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>3700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>1500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>600</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
@@ -5414,63 +5912,75 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-2100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>4800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>4800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-2900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-8900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>3400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
-      </c>
-      <c r="O102" s="3">
-        <v>-600</v>
-      </c>
-      <c r="P102" s="3">
-        <v>2400</v>
       </c>
       <c r="Q102" s="3">
         <v>-600</v>
       </c>
       <c r="R102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="S102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T102" s="3">
         <v>800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-300</v>
       </c>
-      <c r="T102" s="3" t="s">
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PETZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PETZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
   <si>
     <t>PETZ</t>
   </si>
@@ -656,124 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43830</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43646</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43465</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43281</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42916</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42735</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42551</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>200</v>
       </c>
       <c r="E8" s="3">
+        <v>200</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
-        <v>800</v>
-      </c>
       <c r="G8" s="3">
-        <v>800</v>
-      </c>
-      <c r="H8" s="3">
-        <v>800</v>
-      </c>
-      <c r="I8" s="3">
-        <v>800</v>
+        <v>100</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J8" s="3">
         <v>800</v>
@@ -782,60 +789,66 @@
         <v>800</v>
       </c>
       <c r="L8" s="3">
+        <v>800</v>
+      </c>
+      <c r="M8" s="3">
+        <v>800</v>
+      </c>
+      <c r="N8" s="3">
         <v>700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>8000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>12100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>11600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>14900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>14100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>14700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>9700</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3">
         <v>500</v>
@@ -847,99 +860,111 @@
         <v>500</v>
       </c>
       <c r="M9" s="3">
+        <v>500</v>
+      </c>
+      <c r="N9" s="3">
+        <v>500</v>
+      </c>
+      <c r="O9" s="3">
         <v>400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>6800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>7400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>15300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>12400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>10800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>9900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>10400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>7000</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>200</v>
+      </c>
+      <c r="K10" s="3">
+        <v>200</v>
+      </c>
+      <c r="L10" s="3">
         <v>300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="M10" s="3">
         <v>300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="N10" s="3">
         <v>200</v>
       </c>
-      <c r="I10" s="3">
-        <v>200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>300</v>
-      </c>
-      <c r="K10" s="3">
-        <v>300</v>
-      </c>
-      <c r="L10" s="3">
-        <v>200</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>-100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>-2200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>-800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>4100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>4200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>4300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2700</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -962,8 +987,10 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1000,32 +1027,38 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3">
-        <v>0</v>
-      </c>
-      <c r="P12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0</v>
+      </c>
+      <c r="R12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>400</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1086,56 +1119,62 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>1300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>1300</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-200</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>800</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>1600</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1148,8 +1187,14 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1166,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1210,8 +1255,14 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1231,70 +1282,78 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>600</v>
+      </c>
+      <c r="F17" s="3">
         <v>400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>400</v>
       </c>
-      <c r="F17" s="3">
-        <v>3500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>3500</v>
-      </c>
       <c r="H17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J17" s="3">
         <v>1200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1300</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1300</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1900</v>
       </c>
       <c r="M17" s="3">
         <v>1300</v>
       </c>
       <c r="N17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P17" s="3">
         <v>10300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>9300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>20500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>17200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>15300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>13400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>13800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>9500</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1305,16 +1364,16 @@
         <v>-400</v>
       </c>
       <c r="F18" s="3">
-        <v>-2700</v>
+        <v>-400</v>
       </c>
       <c r="G18" s="3">
-        <v>-2700</v>
+        <v>-400</v>
       </c>
       <c r="H18" s="3">
-        <v>-400</v>
+        <v>-2800</v>
       </c>
       <c r="I18" s="3">
-        <v>-400</v>
+        <v>-2800</v>
       </c>
       <c r="J18" s="3">
         <v>-400</v>
@@ -1323,40 +1382,46 @@
         <v>-400</v>
       </c>
       <c r="L18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N18" s="3">
         <v>-1100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-5700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-1300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-5600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>200</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1379,8 +1444,10 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1391,17 +1458,17 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1412,57 +1479,63 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-2500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-2500</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-400</v>
       </c>
       <c r="J21" s="3">
         <v>-400</v>
@@ -1471,40 +1544,46 @@
         <v>-400</v>
       </c>
       <c r="L21" s="3">
-        <v>-1100</v>
+        <v>-400</v>
       </c>
       <c r="M21" s="3">
         <v>-400</v>
       </c>
       <c r="N21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P21" s="3">
         <v>-5800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-5500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>400</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1533,110 +1612,122 @@
         <v>0</v>
       </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>100</v>
+      </c>
+      <c r="F23" s="3">
         <v>800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-4300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-4300</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
         <v>900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-7000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-1700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-5700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>200</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1659,38 +1750,44 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
-      </c>
-      <c r="S24" s="3">
-        <v>100</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
       </c>
       <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <v>100</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1751,70 +1848,82 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>100</v>
+      </c>
+      <c r="F26" s="3">
         <v>800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-4300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-4300</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
       <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
         <v>900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-7000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-4800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>100</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1825,58 +1934,64 @@
         <v>700</v>
       </c>
       <c r="F27" s="3">
+        <v>700</v>
+      </c>
+      <c r="G27" s="3">
+        <v>700</v>
+      </c>
+      <c r="H27" s="3">
         <v>-11800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-11800</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
       <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
         <v>800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-7000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-4800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>100</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1937,49 +2052,55 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>500</v>
+      </c>
+      <c r="E29" s="3">
+        <v>500</v>
+      </c>
+      <c r="F29" s="3">
         <v>-200</v>
       </c>
-      <c r="E29" s="3">
+      <c r="G29" s="3">
         <v>-200</v>
       </c>
-      <c r="F29" s="3">
+      <c r="H29" s="3">
         <v>-7500</v>
       </c>
-      <c r="G29" s="3">
+      <c r="I29" s="3">
         <v>-7500</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>100</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -1999,8 +2120,14 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2061,8 +2188,14 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2123,8 +2256,14 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2135,17 +2274,17 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -2156,37 +2295,43 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2197,58 +2342,64 @@
         <v>700</v>
       </c>
       <c r="F33" s="3">
+        <v>700</v>
+      </c>
+      <c r="G33" s="3">
+        <v>700</v>
+      </c>
+      <c r="H33" s="3">
         <v>-11800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-11800</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
       <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
         <v>800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-7000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-4800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>100</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2309,8 +2460,14 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2321,125 +2478,137 @@
         <v>700</v>
       </c>
       <c r="F35" s="3">
+        <v>700</v>
+      </c>
+      <c r="G35" s="3">
+        <v>700</v>
+      </c>
+      <c r="H35" s="3">
         <v>-11800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-11800</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
       <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
         <v>800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-7000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-4800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>100</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43830</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43646</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43465</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43281</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42916</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42735</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42551</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2462,8 +2631,10 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2486,109 +2657,117 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F41" s="3">
         <v>12900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>12900</v>
       </c>
-      <c r="F41" s="3">
-        <v>13700</v>
-      </c>
-      <c r="G41" s="3">
-        <v>13700</v>
-      </c>
       <c r="H41" s="3">
+        <v>13100</v>
+      </c>
+      <c r="I41" s="3">
+        <v>13100</v>
+      </c>
+      <c r="J41" s="3">
         <v>18000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>18000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>21900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>21900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>12200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>5100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>500</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>13000</v>
+      </c>
+      <c r="F42" s="3">
         <v>12500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>12500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>13300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>13300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>13000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>13000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>9900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>9900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>11600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>8200</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2601,17 +2780,23 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2627,11 +2812,11 @@
       <c r="G43" s="3">
         <v>0</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J43" s="3">
         <v>0</v>
@@ -2643,37 +2828,43 @@
         <v>0</v>
       </c>
       <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>1900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>2300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1700</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2683,11 +2874,11 @@
       <c r="E44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -2695,55 +2886,61 @@
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J44" s="3">
-        <v>0</v>
-      </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
       <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3">
         <v>200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>3000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>3000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>7700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>9100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>9300</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
         <v>200</v>
@@ -2752,10 +2949,10 @@
         <v>200</v>
       </c>
       <c r="H45" s="3">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="I45" s="3">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="J45" s="3">
         <v>2000</v>
@@ -2764,102 +2961,114 @@
         <v>2000</v>
       </c>
       <c r="L45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1700</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>28800</v>
+      </c>
+      <c r="F46" s="3">
         <v>25600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>25600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>27200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>27200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>33000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>33000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>33800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>33800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>25400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>10200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>7200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>8700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>7800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>13700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>15600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>13200</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2890,26 +3099,26 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3">
         <v>100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>100</v>
-      </c>
-      <c r="O47" s="3">
-        <v>200</v>
-      </c>
-      <c r="P47" s="3">
-        <v>200</v>
       </c>
       <c r="Q47" s="3">
         <v>200</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>200</v>
+      </c>
+      <c r="S47" s="3">
+        <v>200</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
@@ -2920,70 +3129,82 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F48" s="3">
         <v>5000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>5000</v>
       </c>
-      <c r="F48" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G48" s="3">
-        <v>1300</v>
-      </c>
       <c r="H48" s="3">
+        <v>700</v>
+      </c>
+      <c r="I48" s="3">
+        <v>700</v>
+      </c>
+      <c r="J48" s="3">
         <v>1400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>6500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>6800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>8600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>8400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>3500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>3200</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2994,16 +3215,16 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>500</v>
@@ -3012,40 +3233,46 @@
         <v>500</v>
       </c>
       <c r="L49" s="3">
+        <v>500</v>
+      </c>
+      <c r="M49" s="3">
+        <v>500</v>
+      </c>
+      <c r="N49" s="3">
         <v>600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>900</v>
-      </c>
-      <c r="N49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="O49" s="3">
-        <v>1000</v>
       </c>
       <c r="P49" s="3">
         <v>1000</v>
       </c>
       <c r="Q49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S49" s="3">
         <v>200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>100</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3106,8 +3333,14 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3168,8 +3401,14 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3186,52 +3425,58 @@
         <v>3</v>
       </c>
       <c r="H52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J52" s="3">
         <v>700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>800</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>1400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>500</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3292,70 +3537,82 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>33300</v>
+      </c>
+      <c r="F54" s="3">
         <v>30600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>30600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>28900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>28900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>35600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>35600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>36500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>36500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>28400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>17700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>15100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>18500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>17400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>18800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>19800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>16600</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3378,8 +3635,10 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3402,28 +3661,30 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>100</v>
+      </c>
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
-        <v>500</v>
-      </c>
-      <c r="G57" s="3">
-        <v>500</v>
-      </c>
       <c r="H57" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="I57" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3">
         <v>500</v>
@@ -3432,274 +3693,298 @@
         <v>500</v>
       </c>
       <c r="L57" s="3">
+        <v>500</v>
+      </c>
+      <c r="M57" s="3">
+        <v>500</v>
+      </c>
+      <c r="N57" s="3">
         <v>3000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>3400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>6200</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>6300</v>
-      </c>
-      <c r="R57" s="3">
-        <v>4700</v>
       </c>
       <c r="S57" s="3">
         <v>6300</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
+      <c r="T57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="U57" s="3">
+        <v>6300</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>800</v>
+      </c>
+      <c r="F58" s="3">
         <v>900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
+        <v>400</v>
+      </c>
+      <c r="I58" s="3">
+        <v>400</v>
+      </c>
+      <c r="J58" s="3">
+        <v>500</v>
+      </c>
+      <c r="K58" s="3">
+        <v>500</v>
+      </c>
+      <c r="L58" s="3">
         <v>600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="M58" s="3">
         <v>600</v>
       </c>
-      <c r="H58" s="3">
-        <v>500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>500</v>
-      </c>
-      <c r="J58" s="3">
-        <v>600</v>
-      </c>
-      <c r="K58" s="3">
-        <v>600</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>6000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>9500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>9500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>15200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>11900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>5100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>3100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>3700</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F59" s="3">
         <v>1300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1300</v>
       </c>
-      <c r="F59" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>2200</v>
-      </c>
       <c r="H59" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2900</v>
+      </c>
+      <c r="J59" s="3">
         <v>11700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>11700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>13500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>13500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>4500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>5000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1100</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F60" s="3">
         <v>2400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>12700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>12700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>14700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>14700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>13500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>17600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>14500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>20700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>19100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>12400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>8700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>11000</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F61" s="3">
         <v>2200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2200</v>
       </c>
-      <c r="F61" s="3">
-        <v>500</v>
-      </c>
-      <c r="G61" s="3">
-        <v>500</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>800</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>200</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3712,8 +3997,14 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3730,10 +4021,10 @@
         <v>3</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
@@ -3741,23 +4032,23 @@
       <c r="K62" s="3">
         <v>0</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
+      <c r="L62" s="3">
+        <v>0</v>
       </c>
       <c r="M62" s="3">
-        <v>300</v>
-      </c>
-      <c r="N62" s="3">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O62" s="3">
         <v>300</v>
       </c>
       <c r="P62" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q62" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -3765,17 +4056,23 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3836,8 +4133,14 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3898,8 +4201,14 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3960,70 +4269,82 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F66" s="3">
         <v>4500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>13300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>13300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>15400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>15400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>14300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>17900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>14700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>21300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>19400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>12400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>8700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>11000</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4046,8 +4367,10 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4108,8 +4431,14 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4170,8 +4499,14 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4232,8 +4567,14 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4294,70 +4635,82 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-25300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-25300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-26600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-26600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-27900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-27900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-28000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-28000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-29700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-22400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-21800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-14900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-3800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>1400</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4418,8 +4771,14 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4480,8 +4839,14 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4542,70 +4907,82 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>27300</v>
+      </c>
+      <c r="F76" s="3">
         <v>25900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>25900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>24600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>24600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>21900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>21900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>20700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>20700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>13500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-2700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>6500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>11100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>5600</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4666,75 +5043,87 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43830</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43646</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43465</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43281</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42916</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42735</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42551</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4745,58 +5134,64 @@
         <v>700</v>
       </c>
       <c r="F81" s="3">
+        <v>700</v>
+      </c>
+      <c r="G81" s="3">
+        <v>700</v>
+      </c>
+      <c r="H81" s="3">
         <v>-11800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-11800</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
       <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3">
         <v>800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-7000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-4800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>100</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4819,52 +5214,54 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>-400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>300</v>
-      </c>
-      <c r="P83" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>200</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
@@ -4873,16 +5270,22 @@
         <v>200</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U83" s="3">
         <v>200</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>100</v>
+      </c>
+      <c r="W83" s="3">
+        <v>200</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4943,8 +5346,14 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5005,8 +5414,14 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5067,8 +5482,14 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5129,8 +5550,14 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5191,70 +5618,82 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>4800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-4700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-2000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-1500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-600</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5277,28 +5716,30 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
@@ -5309,38 +5750,44 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-6400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5401,8 +5848,14 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5463,8 +5916,14 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5475,58 +5934,64 @@
         <v>700</v>
       </c>
       <c r="F94" s="3">
+        <v>700</v>
+      </c>
+      <c r="G94" s="3">
+        <v>700</v>
+      </c>
+      <c r="H94" s="3">
         <v>-2000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-2000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>2400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>2400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-3000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-4600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>1200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5549,8 +6014,10 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5581,11 +6048,11 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -5611,8 +6078,14 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5673,8 +6146,14 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5735,8 +6214,14 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5797,8 +6282,14 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5808,107 +6299,113 @@
       <c r="E100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3">
         <v>1000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1000</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>3000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>3000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>-9400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>4200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>5300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>6000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>1700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>3700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>1500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>600</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
@@ -5918,69 +6415,81 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>4800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>4800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-2900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-8900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>3400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>-600</v>
-      </c>
-      <c r="R102" s="3">
-        <v>2400</v>
       </c>
       <c r="S102" s="3">
         <v>-600</v>
       </c>
       <c r="T102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="U102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="V102" s="3">
         <v>800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-300</v>
       </c>
-      <c r="V102" s="3" t="s">
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PETZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PETZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
   <si>
     <t>PETZ</t>
   </si>
@@ -770,11 +770,11 @@
       <c r="E8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
-        <v>100</v>
-      </c>
-      <c r="G8" s="3">
-        <v>100</v>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -782,8 +782,8 @@
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J8" s="3">
-        <v>800</v>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>800</v>
@@ -838,11 +838,11 @@
       <c r="E9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
@@ -850,8 +850,8 @@
       <c r="I9" s="3">
         <v>0</v>
       </c>
-      <c r="J9" s="3">
-        <v>500</v>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K9" s="3">
         <v>500</v>
@@ -906,11 +906,11 @@
       <c r="E10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
@@ -918,8 +918,8 @@
       <c r="I10" s="3">
         <v>0</v>
       </c>
-      <c r="J10" s="3">
-        <v>200</v>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K10" s="3">
         <v>200</v>
@@ -1136,11 +1136,11 @@
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3">
-        <v>200</v>
-      </c>
-      <c r="G14" s="3">
-        <v>200</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
         <v>1300</v>
@@ -1295,11 +1295,11 @@
       <c r="E17" s="3">
         <v>600</v>
       </c>
-      <c r="F17" s="3">
-        <v>400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>400</v>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H17" s="3">
         <v>2800</v>
@@ -1307,8 +1307,8 @@
       <c r="I17" s="3">
         <v>2800</v>
       </c>
-      <c r="J17" s="3">
-        <v>1200</v>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K17" s="3">
         <v>1200</v>
@@ -1363,11 +1363,11 @@
       <c r="E18" s="3">
         <v>-400</v>
       </c>
-      <c r="F18" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-400</v>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H18" s="3">
         <v>-2800</v>
@@ -1375,8 +1375,8 @@
       <c r="I18" s="3">
         <v>-2800</v>
       </c>
-      <c r="J18" s="3">
-        <v>-400</v>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K18" s="3">
         <v>-400</v>
@@ -1457,11 +1457,11 @@
       <c r="E20" s="3">
         <v>0</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
         <v>-200</v>
@@ -1469,8 +1469,8 @@
       <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1526,10 +1526,10 @@
         <v>-400</v>
       </c>
       <c r="F21" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <v>-2500</v>
@@ -1538,7 +1538,7 @@
         <v>-2500</v>
       </c>
       <c r="J21" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>-400</v>
@@ -1593,11 +1593,11 @@
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1605,8 +1605,8 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1661,11 +1661,11 @@
       <c r="E23" s="3">
         <v>100</v>
       </c>
-      <c r="F23" s="3">
-        <v>800</v>
-      </c>
-      <c r="G23" s="3">
-        <v>800</v>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H23" s="3">
         <v>-4300</v>
@@ -1673,8 +1673,8 @@
       <c r="I23" s="3">
         <v>-4300</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -1865,11 +1865,11 @@
       <c r="E26" s="3">
         <v>100</v>
       </c>
-      <c r="F26" s="3">
-        <v>800</v>
-      </c>
-      <c r="G26" s="3">
-        <v>800</v>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H26" s="3">
         <v>-4300</v>
@@ -1877,8 +1877,8 @@
       <c r="I26" s="3">
         <v>-4300</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -1933,11 +1933,11 @@
       <c r="E27" s="3">
         <v>700</v>
       </c>
-      <c r="F27" s="3">
-        <v>700</v>
-      </c>
-      <c r="G27" s="3">
-        <v>700</v>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H27" s="3">
         <v>-11800</v>
@@ -1945,8 +1945,8 @@
       <c r="I27" s="3">
         <v>-11800</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -2070,10 +2070,10 @@
         <v>500</v>
       </c>
       <c r="F29" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>-7500</v>
@@ -2273,11 +2273,11 @@
       <c r="E32" s="3">
         <v>0</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
         <v>200</v>
@@ -2285,8 +2285,8 @@
       <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2341,11 +2341,11 @@
       <c r="E33" s="3">
         <v>700</v>
       </c>
-      <c r="F33" s="3">
-        <v>700</v>
-      </c>
-      <c r="G33" s="3">
-        <v>700</v>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H33" s="3">
         <v>-11800</v>
@@ -2353,8 +2353,8 @@
       <c r="I33" s="3">
         <v>-11800</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K33" s="3">
         <v>0</v>
@@ -2477,11 +2477,11 @@
       <c r="E35" s="3">
         <v>700</v>
       </c>
-      <c r="F35" s="3">
-        <v>700</v>
-      </c>
-      <c r="G35" s="3">
-        <v>700</v>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H35" s="3">
         <v>-11800</v>
@@ -2489,8 +2489,8 @@
       <c r="I35" s="3">
         <v>-11800</v>
       </c>
-      <c r="J35" s="3">
-        <v>0</v>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K35" s="3">
         <v>0</v>
@@ -2670,11 +2670,11 @@
       <c r="E41" s="3">
         <v>15700</v>
       </c>
-      <c r="F41" s="3">
-        <v>12900</v>
-      </c>
-      <c r="G41" s="3">
-        <v>12900</v>
+      <c r="F41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H41" s="3">
         <v>13100</v>
@@ -2682,8 +2682,8 @@
       <c r="I41" s="3">
         <v>13100</v>
       </c>
-      <c r="J41" s="3">
-        <v>18000</v>
+      <c r="J41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K41" s="3">
         <v>18000</v>
@@ -2739,10 +2739,10 @@
         <v>13000</v>
       </c>
       <c r="F42" s="3">
-        <v>12500</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>12500</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>13300</v>
@@ -2751,7 +2751,7 @@
         <v>13300</v>
       </c>
       <c r="J42" s="3">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>13000</v>
@@ -2806,11 +2806,11 @@
       <c r="E43" s="3">
         <v>0</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -2818,8 +2818,8 @@
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2942,11 +2942,11 @@
       <c r="E45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
-        <v>200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>200</v>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
         <v>800</v>
@@ -2954,8 +2954,8 @@
       <c r="I45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3">
-        <v>2000</v>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>2000</v>
@@ -3010,11 +3010,11 @@
       <c r="E46" s="3">
         <v>28800</v>
       </c>
-      <c r="F46" s="3">
-        <v>25600</v>
-      </c>
-      <c r="G46" s="3">
-        <v>25600</v>
+      <c r="F46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H46" s="3">
         <v>27200</v>
@@ -3022,8 +3022,8 @@
       <c r="I46" s="3">
         <v>27200</v>
       </c>
-      <c r="J46" s="3">
-        <v>33000</v>
+      <c r="J46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K46" s="3">
         <v>33000</v>
@@ -3146,11 +3146,11 @@
       <c r="E48" s="3">
         <v>4500</v>
       </c>
-      <c r="F48" s="3">
-        <v>5000</v>
-      </c>
-      <c r="G48" s="3">
-        <v>5000</v>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3">
         <v>700</v>
@@ -3158,8 +3158,8 @@
       <c r="I48" s="3">
         <v>700</v>
       </c>
-      <c r="J48" s="3">
-        <v>1400</v>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>1400</v>
@@ -3214,11 +3214,11 @@
       <c r="E49" s="3">
         <v>0</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
+      <c r="F49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
@@ -3226,8 +3226,8 @@
       <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="J49" s="3">
-        <v>500</v>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3">
         <v>500</v>
@@ -3430,8 +3430,8 @@
       <c r="I52" s="3">
         <v>1000</v>
       </c>
-      <c r="J52" s="3">
-        <v>700</v>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>700</v>
@@ -3554,11 +3554,11 @@
       <c r="E54" s="3">
         <v>33300</v>
       </c>
-      <c r="F54" s="3">
-        <v>30600</v>
-      </c>
-      <c r="G54" s="3">
-        <v>30600</v>
+      <c r="F54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H54" s="3">
         <v>28900</v>
@@ -3566,8 +3566,8 @@
       <c r="I54" s="3">
         <v>28900</v>
       </c>
-      <c r="J54" s="3">
-        <v>35600</v>
+      <c r="J54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K54" s="3">
         <v>35600</v>
@@ -3674,11 +3674,11 @@
       <c r="E57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
-        <v>200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>200</v>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H57" s="3">
         <v>100</v>
@@ -3686,8 +3686,8 @@
       <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
-        <v>500</v>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3">
         <v>500</v>
@@ -3742,11 +3742,11 @@
       <c r="E58" s="3">
         <v>800</v>
       </c>
-      <c r="F58" s="3">
-        <v>900</v>
-      </c>
-      <c r="G58" s="3">
-        <v>900</v>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H58" s="3">
         <v>400</v>
@@ -3754,8 +3754,8 @@
       <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="J58" s="3">
-        <v>500</v>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3">
         <v>500</v>
@@ -3810,11 +3810,11 @@
       <c r="E59" s="3">
         <v>3200</v>
       </c>
-      <c r="F59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1300</v>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3">
         <v>2900</v>
@@ -3822,8 +3822,8 @@
       <c r="I59" s="3">
         <v>2900</v>
       </c>
-      <c r="J59" s="3">
-        <v>11700</v>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>11700</v>
@@ -3878,11 +3878,11 @@
       <c r="E60" s="3">
         <v>4200</v>
       </c>
-      <c r="F60" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G60" s="3">
-        <v>2400</v>
+      <c r="F60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H60" s="3">
         <v>3400</v>
@@ -3890,8 +3890,8 @@
       <c r="I60" s="3">
         <v>3400</v>
       </c>
-      <c r="J60" s="3">
-        <v>12700</v>
+      <c r="J60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K60" s="3">
         <v>12700</v>
@@ -3947,10 +3947,10 @@
         <v>1700</v>
       </c>
       <c r="F61" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -3959,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>600</v>
@@ -4026,8 +4026,8 @@
       <c r="I62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -4286,11 +4286,11 @@
       <c r="E66" s="3">
         <v>5900</v>
       </c>
-      <c r="F66" s="3">
-        <v>4500</v>
-      </c>
-      <c r="G66" s="3">
-        <v>4500</v>
+      <c r="F66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H66" s="3">
         <v>3900</v>
@@ -4298,8 +4298,8 @@
       <c r="I66" s="3">
         <v>3900</v>
       </c>
-      <c r="J66" s="3">
-        <v>13300</v>
+      <c r="J66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K66" s="3">
         <v>13300</v>
@@ -4652,11 +4652,11 @@
       <c r="E72" s="3">
         <v>-23900</v>
       </c>
-      <c r="F72" s="3">
-        <v>-25300</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-25300</v>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H72" s="3">
         <v>-26600</v>
@@ -4664,8 +4664,8 @@
       <c r="I72" s="3">
         <v>-26600</v>
       </c>
-      <c r="J72" s="3">
-        <v>-27900</v>
+      <c r="J72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K72" s="3">
         <v>-27900</v>
@@ -4924,11 +4924,11 @@
       <c r="E76" s="3">
         <v>27300</v>
       </c>
-      <c r="F76" s="3">
-        <v>25900</v>
-      </c>
-      <c r="G76" s="3">
-        <v>25900</v>
+      <c r="F76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H76" s="3">
         <v>24600</v>
@@ -4936,8 +4936,8 @@
       <c r="I76" s="3">
         <v>24600</v>
       </c>
-      <c r="J76" s="3">
-        <v>21900</v>
+      <c r="J76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K76" s="3">
         <v>21900</v>
@@ -5133,11 +5133,11 @@
       <c r="E81" s="3">
         <v>700</v>
       </c>
-      <c r="F81" s="3">
-        <v>700</v>
-      </c>
-      <c r="G81" s="3">
-        <v>700</v>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H81" s="3">
         <v>-11800</v>
@@ -5145,8 +5145,8 @@
       <c r="I81" s="3">
         <v>-11800</v>
       </c>
-      <c r="J81" s="3">
-        <v>0</v>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K81" s="3">
         <v>0</v>
@@ -5227,11 +5227,11 @@
       <c r="E83" s="3">
         <v>1400</v>
       </c>
-      <c r="F83" s="3">
-        <v>100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>100</v>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H83" s="3">
         <v>-100</v>
@@ -5239,8 +5239,8 @@
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -5635,11 +5635,11 @@
       <c r="E89" s="3">
         <v>1100</v>
       </c>
-      <c r="F89" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-1200</v>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H89" s="3">
         <v>-100</v>
@@ -5647,8 +5647,8 @@
       <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
-        <v>-1200</v>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K89" s="3">
         <v>-1200</v>
@@ -5729,11 +5729,11 @@
       <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-900</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -5933,11 +5933,11 @@
       <c r="E94" s="3">
         <v>700</v>
       </c>
-      <c r="F94" s="3">
-        <v>700</v>
-      </c>
-      <c r="G94" s="3">
-        <v>700</v>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H94" s="3">
         <v>-2000</v>
@@ -5945,8 +5945,8 @@
       <c r="I94" s="3">
         <v>-2000</v>
       </c>
-      <c r="J94" s="3">
-        <v>-1100</v>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>-1100</v>
@@ -6367,11 +6367,11 @@
       <c r="E101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
-        <v>300</v>
-      </c>
-      <c r="G101" s="3">
-        <v>300</v>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H101" s="3">
         <v>-1300</v>
@@ -6379,8 +6379,8 @@
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3">
-        <v>500</v>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>500</v>
@@ -6436,10 +6436,10 @@
         <v>1400</v>
       </c>
       <c r="F102" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
         <v>-2100</v>
@@ -6448,7 +6448,7 @@
         <v>-2100</v>
       </c>
       <c r="J102" s="3">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="K102" s="3">
         <v>-2000</v>

--- a/AAII_Financials/Quarterly/PETZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PETZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
   <si>
     <t>PETZ</t>
   </si>
@@ -656,127 +656,133 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43646</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43465</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43281</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43100</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42916</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42735</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42551</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>300</v>
+      </c>
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="3">
-        <v>800</v>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -784,76 +790,82 @@
       <c r="K8" s="3">
         <v>800</v>
       </c>
-      <c r="L8" s="3">
-        <v>800</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>800</v>
       </c>
       <c r="N8" s="3">
+        <v>800</v>
+      </c>
+      <c r="O8" s="3">
+        <v>800</v>
+      </c>
+      <c r="P8" s="3">
         <v>700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>4600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>8000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>12100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>11600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>14900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>14100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>14700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>9700</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>400</v>
+      </c>
+      <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
       <c r="H9" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
         <v>-1400</v>
-      </c>
-      <c r="I9" s="3">
-        <v>500</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K9" s="3">
         <v>500</v>
       </c>
-      <c r="L9" s="3">
-        <v>500</v>
+      <c r="L9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M9" s="3">
         <v>500</v>
@@ -862,105 +874,117 @@
         <v>500</v>
       </c>
       <c r="O9" s="3">
+        <v>500</v>
+      </c>
+      <c r="P9" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q9" s="3">
         <v>400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>6800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>7400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>15300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>12400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>10800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>9900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>10400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>7000</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
       <c r="H10" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
         <v>-800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>300</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3">
         <v>200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>-100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>-3200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>-800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>4100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>4200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>4300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>2700</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -985,8 +1009,10 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1029,32 +1055,38 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3">
-        <v>0</v>
-      </c>
-      <c r="R12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3">
         <v>100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>400</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1121,62 +1153,68 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>1300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>1300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-200</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>800</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
         <v>1600</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1189,38 +1227,44 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
         <v>100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1257,8 +1301,14 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1280,144 +1330,158 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F17" s="3">
         <v>600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I17" s="3">
         <v>2800</v>
       </c>
-      <c r="G17" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>-1900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1300</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3">
         <v>1200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1300</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1300</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1900</v>
       </c>
       <c r="O17" s="3">
         <v>1300</v>
       </c>
       <c r="P17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R17" s="3">
         <v>10300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>9300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>20500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>17200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>15300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>13400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>13800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>9500</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-2800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K18" s="3">
         <v>-400</v>
       </c>
-      <c r="L18" s="3">
-        <v>-400</v>
+      <c r="L18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M18" s="3">
         <v>-400</v>
       </c>
       <c r="N18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P18" s="3">
         <v>-1100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-1000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-8400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-5600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>200</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1442,37 +1506,39 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="F20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1481,113 +1547,125 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-400</v>
+        <v>-5000</v>
       </c>
       <c r="E21" s="3">
-        <v>-400</v>
+        <v>-5000</v>
       </c>
       <c r="F21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="I21" s="3">
         <v>-2500</v>
       </c>
-      <c r="G21" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J21" s="3">
-        <v>100</v>
       </c>
       <c r="K21" s="3">
         <v>-400</v>
       </c>
       <c r="L21" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="M21" s="3">
         <v>-400</v>
       </c>
       <c r="N21" s="3">
-        <v>-1100</v>
+        <v>-400</v>
       </c>
       <c r="O21" s="3">
         <v>-400</v>
       </c>
       <c r="P21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R21" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-8100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-5500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>400</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1596,140 +1674,152 @@
         <v>0</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>-500</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>200</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
       <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>200</v>
+      </c>
+      <c r="F23" s="3">
         <v>100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="I23" s="3">
         <v>-4300</v>
       </c>
-      <c r="G23" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>900</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
         <v>900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-8500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-5700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>200</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1752,38 +1842,44 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-100</v>
-      </c>
-      <c r="U24" s="3">
-        <v>100</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
       </c>
       <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1850,144 +1946,162 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>200</v>
+      </c>
+      <c r="F26" s="3">
         <v>100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="I26" s="3">
         <v>-4300</v>
       </c>
-      <c r="G26" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>900</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
         <v>900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-9400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-4800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>100</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>200</v>
+      </c>
+      <c r="F27" s="3">
         <v>700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-11800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-11800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>800</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
         <v>800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-9400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-4800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>100</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2054,55 +2168,61 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>500</v>
       </c>
-      <c r="E29" s="3">
+      <c r="G29" s="3">
         <v>500</v>
       </c>
-      <c r="F29" s="3">
+      <c r="H29" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="I29" s="3">
         <v>-7500</v>
       </c>
-      <c r="G29" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="H29" s="3">
+      <c r="J29" s="3">
         <v>-400</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>100</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>100</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2122,8 +2242,14 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2190,8 +2316,14 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2258,37 +2390,43 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-4400</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-4400</v>
       </c>
       <c r="F32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2297,105 +2435,117 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>200</v>
+      </c>
+      <c r="F33" s="3">
         <v>700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-11800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-11800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>800</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-9400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-4800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>100</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2462,149 +2612,167 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>200</v>
+      </c>
+      <c r="F35" s="3">
         <v>700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-11800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-11800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>800</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-9400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-4800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>100</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43646</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43465</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43281</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43100</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42916</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42735</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42551</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2629,8 +2797,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2655,121 +2825,129 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>19100</v>
+      </c>
+      <c r="F41" s="3">
         <v>15700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>15700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>13100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>13100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>21900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>21900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>18000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>18000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>21900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>21900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>12200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>5100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>500</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>14500</v>
+      </c>
+      <c r="F42" s="3">
         <v>13000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>13000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>13300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>13300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>9900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>9900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>4400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>13000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>9900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>9900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>11600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>8200</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2782,37 +2960,43 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
-      </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J43" s="3">
         <v>0</v>
@@ -2830,37 +3014,43 @@
         <v>0</v>
       </c>
       <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>100</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
         <v>1900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>2100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>2300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1700</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2876,195 +3066,213 @@
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3">
         <v>100</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
       <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
         <v>200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>3000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>3000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>7700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>9100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>9300</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>2000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>8500</v>
       </c>
       <c r="K45" s="3">
         <v>2000</v>
       </c>
       <c r="L45" s="3">
-        <v>2000</v>
+        <v>8500</v>
       </c>
       <c r="M45" s="3">
         <v>2000</v>
       </c>
       <c r="N45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>2600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>2400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1700</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>34100</v>
+      </c>
+      <c r="F46" s="3">
         <v>28800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>28800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>27200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>27200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>33800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>33800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>31100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>33000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>33800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>33800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>25400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>10200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>7200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>8700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>7800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>13700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>15600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>13200</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3101,26 +3309,26 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>100</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>200</v>
-      </c>
-      <c r="R47" s="3">
-        <v>200</v>
       </c>
       <c r="S47" s="3">
         <v>200</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
+      <c r="T47" s="3">
+        <v>200</v>
+      </c>
+      <c r="U47" s="3">
+        <v>200</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
@@ -3131,76 +3339,88 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F48" s="3">
         <v>4500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>5400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>6500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>6800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>8600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>8400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>3400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>3500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>3200</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3217,10 +3437,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>500</v>
@@ -3235,40 +3455,46 @@
         <v>500</v>
       </c>
       <c r="N49" s="3">
+        <v>500</v>
+      </c>
+      <c r="O49" s="3">
+        <v>500</v>
+      </c>
+      <c r="P49" s="3">
         <v>600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>900</v>
-      </c>
-      <c r="P49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>1000</v>
       </c>
       <c r="R49" s="3">
         <v>1000</v>
       </c>
       <c r="S49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U49" s="3">
         <v>200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>100</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3335,8 +3561,14 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3403,8 +3635,14 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3414,65 +3652,71 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
         <v>1000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>800</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
         <v>1400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>500</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3539,76 +3783,88 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>40300</v>
+      </c>
+      <c r="F54" s="3">
         <v>33300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>33300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>28900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>28900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>36500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>36500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>37900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>35600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>36500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>36500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>28400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>17700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>15100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>18500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>17400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>18800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>19800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>16600</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3633,8 +3889,10 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3659,8 +3917,10 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3677,10 +3937,10 @@
         <v>100</v>
       </c>
       <c r="H57" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="I57" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3">
         <v>500</v>
@@ -3695,298 +3955,322 @@
         <v>500</v>
       </c>
       <c r="N57" s="3">
+        <v>500</v>
+      </c>
+      <c r="O57" s="3">
+        <v>500</v>
+      </c>
+      <c r="P57" s="3">
         <v>3000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>3400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>3800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>6200</v>
-      </c>
-      <c r="S57" s="3">
-        <v>6300</v>
-      </c>
-      <c r="T57" s="3">
-        <v>4700</v>
       </c>
       <c r="U57" s="3">
         <v>6300</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
+      <c r="V57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="W57" s="3">
+        <v>6300</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>900</v>
+      </c>
+      <c r="F58" s="3">
         <v>800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>600</v>
-      </c>
-      <c r="I58" s="3">
-        <v>600</v>
       </c>
       <c r="J58" s="3">
         <v>600</v>
       </c>
       <c r="K58" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="L58" s="3">
         <v>600</v>
       </c>
       <c r="M58" s="3">
+        <v>500</v>
+      </c>
+      <c r="N58" s="3">
         <v>600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
+        <v>600</v>
+      </c>
+      <c r="P58" s="3">
         <v>6000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>9500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>9500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>15200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>11900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>5100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>3100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>3700</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F59" s="3">
         <v>3200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>13500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>13500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>18500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>11700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>13500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>13500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>4500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>5000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1100</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F60" s="3">
         <v>4200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>14700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>14700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>19700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>12700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>14700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>14700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>13500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>17600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>14500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>20700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>19100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>12400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>8700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>11000</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F61" s="3">
         <v>1700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1700</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>4800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>800</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>200</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -3999,8 +4283,14 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4010,18 +4300,18 @@
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
       <c r="J62" s="3">
         <v>0</v>
       </c>
@@ -4034,23 +4324,23 @@
       <c r="M62" s="3">
         <v>0</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
+      <c r="N62" s="3">
+        <v>0</v>
       </c>
       <c r="O62" s="3">
-        <v>300</v>
-      </c>
-      <c r="P62" s="3">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q62" s="3">
         <v>300</v>
       </c>
       <c r="R62" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="S62" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
@@ -4058,17 +4348,23 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4135,8 +4431,14 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4203,8 +4505,14 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4271,76 +4579,88 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>9600</v>
+      </c>
+      <c r="F66" s="3">
         <v>5900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>15400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>15400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>24500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>13300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>15400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>15400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>14300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>17900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>14700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>21300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>19400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>12400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>8700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>11000</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4365,8 +4685,10 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4433,8 +4755,14 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4501,8 +4829,14 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4569,8 +4903,14 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4637,76 +4977,88 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-23900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-23900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-26600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-26600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-28000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-28000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-28800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-27900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-28000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-28000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-29700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-22400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-21800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-14900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-13200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-3800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>1000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1400</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4773,8 +5125,14 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4841,8 +5199,14 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4909,76 +5273,88 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>30600</v>
+      </c>
+      <c r="F76" s="3">
         <v>27300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>27300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>24600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>24600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>20700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>20700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>13000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>21900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>20700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>20700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>13500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-2700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-1900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>6500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>11100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>5600</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5045,149 +5421,167 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43646</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43465</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43281</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43100</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42916</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42735</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42551</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>200</v>
+      </c>
+      <c r="F81" s="3">
         <v>700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-11800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-11800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>800</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-9400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-4800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>100</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5212,58 +5606,60 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F83" s="3">
         <v>-100</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
+      <c r="G83" s="3">
+        <v>0</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>-400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>300</v>
-      </c>
-      <c r="R83" s="3">
-        <v>200</v>
-      </c>
-      <c r="S83" s="3">
-        <v>200</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
@@ -5272,16 +5668,22 @@
         <v>200</v>
       </c>
       <c r="V83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W83" s="3">
         <v>200</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5348,8 +5750,14 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5416,8 +5824,14 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5484,8 +5898,14 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5552,8 +5972,14 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5620,76 +6046,88 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F89" s="3">
         <v>1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="P89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>4800</v>
+      </c>
+      <c r="R89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="S89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="T89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="U89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="V89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="W89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-600</v>
       </c>
-      <c r="I89" s="3">
-        <v>-600</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-600</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-600</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-400</v>
-      </c>
-      <c r="O89" s="3">
-        <v>4800</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-900</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-900</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-600</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5714,8 +6152,10 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5726,16 +6166,16 @@
         <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
@@ -5752,38 +6192,44 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-6400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-5600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5850,8 +6296,14 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5918,76 +6370,88 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F94" s="3">
         <v>700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-2000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-2000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>2400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>2400</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
         <v>-1100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>2400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>2400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-3000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-4600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-6300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-1100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>1200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-200</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6012,8 +6476,10 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6050,11 +6516,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6080,8 +6546,14 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6148,8 +6620,14 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6216,8 +6694,14 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6284,130 +6768,142 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="D100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I100" s="3">
         <v>1000</v>
       </c>
-      <c r="G100" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>3000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>3000</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>3000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>3000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-9400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>4200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>5300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>6000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>1700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>3700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>1500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>600</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1300</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
+      <c r="G101" s="3">
+        <v>0</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
@@ -6417,75 +6913,87 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F102" s="3">
         <v>1400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>3500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>4800</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-2000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>4800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>4800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-2900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-8900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>3400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-300</v>
-      </c>
-      <c r="S102" s="3">
-        <v>-600</v>
-      </c>
-      <c r="T102" s="3">
-        <v>2400</v>
       </c>
       <c r="U102" s="3">
         <v>-600</v>
       </c>
       <c r="V102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="W102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X102" s="3">
         <v>800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-300</v>
       </c>
-      <c r="X102" s="3" t="s">
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
